--- a/DATA/canonical/GDP_ANNUAL.xlsx
+++ b/DATA/canonical/GDP_ANNUAL.xlsx
@@ -486,7 +486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -573,16 +573,33 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B6" t="str">
+        <v>ძირითადი კაპიტალის მთლიანი ფორმირება (აქტივების მიხედვით)</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Gross fixed capital formation by asset type</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -873,9 +890,111 @@
         <v>16</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="B18" t="str">
+        <v>საცხოვრებელი დანიშნულების შენობები</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Dwellings</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="B19" t="str">
+        <v>არასაცხოვრებელი დანიშნულების და სხვა ნაგებობები</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Other buildings and structures</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="B20" t="str">
+        <v>მანქანა, მოწყობილობები და სამხედრო აღჭურვილობა</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Machinery, equipment and weapons systems</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="B21" t="str">
+        <v>კულტივირებული ბიოლოგიური აქტივები</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Cultivated biological resources</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="B22" t="str">
+        <v>ინტელექტუალური საკუთრების პროდუქტები და არაწარმოებულ აქტივებზე საკუთრების გადაცემის ხარჯები</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Intellectual property products</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="B23" t="str">
+        <v>დაუკვირვებადი დამატებული ღირებულების წილი მთლიან დამატებულ ღირებულებაში</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Non-observed economy share in total gross value added</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E23"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -927,7 +1046,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G289"/>
+  <dimension ref="A1:G385"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7576,9 +7695,2217 @@
         <v>add</v>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B290" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C290" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D290" t="str">
+        <v>2010</v>
+      </c>
+      <c r="E290">
+        <v>315.7</v>
+      </c>
+      <c r="F290" t="str">
+        <v>A</v>
+      </c>
+      <c r="G290" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B291" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C291" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D291" t="str">
+        <v>2011</v>
+      </c>
+      <c r="E291">
+        <v>587.8</v>
+      </c>
+      <c r="F291" t="str">
+        <v>A</v>
+      </c>
+      <c r="G291" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B292" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C292" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D292" t="str">
+        <v>2012</v>
+      </c>
+      <c r="E292">
+        <v>896.4</v>
+      </c>
+      <c r="F292" t="str">
+        <v>A</v>
+      </c>
+      <c r="G292" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B293" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C293" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D293" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E293">
+        <v>850.2</v>
+      </c>
+      <c r="F293" t="str">
+        <v>A</v>
+      </c>
+      <c r="G293" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B294" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C294" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D294" t="str">
+        <v>2014</v>
+      </c>
+      <c r="E294">
+        <v>1422.8</v>
+      </c>
+      <c r="F294" t="str">
+        <v>A</v>
+      </c>
+      <c r="G294" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B295" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C295" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D295" t="str">
+        <v>2015</v>
+      </c>
+      <c r="E295">
+        <v>1193.6</v>
+      </c>
+      <c r="F295" t="str">
+        <v>A</v>
+      </c>
+      <c r="G295" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B296" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C296" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D296" t="str">
+        <v>2016</v>
+      </c>
+      <c r="E296">
+        <v>1917.2</v>
+      </c>
+      <c r="F296" t="str">
+        <v>A</v>
+      </c>
+      <c r="G296" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B297" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C297" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D297" t="str">
+        <v>2017</v>
+      </c>
+      <c r="E297">
+        <v>1568.4</v>
+      </c>
+      <c r="F297" t="str">
+        <v>A</v>
+      </c>
+      <c r="G297" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B298" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C298" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D298" t="str">
+        <v>2018</v>
+      </c>
+      <c r="E298">
+        <v>2289.5</v>
+      </c>
+      <c r="F298" t="str">
+        <v>A</v>
+      </c>
+      <c r="G298" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B299" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C299" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D299" t="str">
+        <v>2019</v>
+      </c>
+      <c r="E299">
+        <v>2495.8</v>
+      </c>
+      <c r="F299" t="str">
+        <v>A</v>
+      </c>
+      <c r="G299" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B300" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C300" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D300" t="str">
+        <v>2020</v>
+      </c>
+      <c r="E300">
+        <v>1487.8</v>
+      </c>
+      <c r="F300" t="str">
+        <v>A</v>
+      </c>
+      <c r="G300" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B301" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C301" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D301" t="str">
+        <v>2021</v>
+      </c>
+      <c r="E301">
+        <v>1496.8</v>
+      </c>
+      <c r="F301" t="str">
+        <v>A</v>
+      </c>
+      <c r="G301" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B302" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C302" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D302" t="str">
+        <v>2022</v>
+      </c>
+      <c r="E302">
+        <v>2655.4</v>
+      </c>
+      <c r="F302" t="str">
+        <v>A</v>
+      </c>
+      <c r="G302" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B303" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C303" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D303" t="str">
+        <v>2023</v>
+      </c>
+      <c r="E303">
+        <v>3858.8</v>
+      </c>
+      <c r="F303" t="str">
+        <v>A</v>
+      </c>
+      <c r="G303" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B304" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C304" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D304" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E304">
+        <v>4626.8</v>
+      </c>
+      <c r="F304" t="str">
+        <v>A</v>
+      </c>
+      <c r="G304" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B305" t="str">
+        <v>gfcf-dwellings</v>
+      </c>
+      <c r="C305" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D305" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E305">
+        <v>4297</v>
+      </c>
+      <c r="F305" t="str">
+        <v>P</v>
+      </c>
+      <c r="G305" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B306" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C306" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D306" t="str">
+        <v>2010</v>
+      </c>
+      <c r="E306">
+        <v>2234.8</v>
+      </c>
+      <c r="F306" t="str">
+        <v>A</v>
+      </c>
+      <c r="G306" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B307" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C307" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D307" t="str">
+        <v>2011</v>
+      </c>
+      <c r="E307">
+        <v>2359</v>
+      </c>
+      <c r="F307" t="str">
+        <v>A</v>
+      </c>
+      <c r="G307" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B308" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C308" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D308" t="str">
+        <v>2012</v>
+      </c>
+      <c r="E308">
+        <v>2449.4</v>
+      </c>
+      <c r="F308" t="str">
+        <v>A</v>
+      </c>
+      <c r="G308" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B309" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C309" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D309" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E309">
+        <v>1996.7</v>
+      </c>
+      <c r="F309" t="str">
+        <v>A</v>
+      </c>
+      <c r="G309" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B310" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C310" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D310" t="str">
+        <v>2014</v>
+      </c>
+      <c r="E310">
+        <v>2299.7</v>
+      </c>
+      <c r="F310" t="str">
+        <v>A</v>
+      </c>
+      <c r="G310" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B311" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C311" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D311" t="str">
+        <v>2015</v>
+      </c>
+      <c r="E311">
+        <v>2984.8</v>
+      </c>
+      <c r="F311" t="str">
+        <v>A</v>
+      </c>
+      <c r="G311" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B312" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C312" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D312" t="str">
+        <v>2016</v>
+      </c>
+      <c r="E312">
+        <v>2931.4</v>
+      </c>
+      <c r="F312" t="str">
+        <v>A</v>
+      </c>
+      <c r="G312" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B313" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C313" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D313" t="str">
+        <v>2017</v>
+      </c>
+      <c r="E313">
+        <v>3181.2</v>
+      </c>
+      <c r="F313" t="str">
+        <v>A</v>
+      </c>
+      <c r="G313" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B314" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C314" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D314" t="str">
+        <v>2018</v>
+      </c>
+      <c r="E314">
+        <v>3760</v>
+      </c>
+      <c r="F314" t="str">
+        <v>A</v>
+      </c>
+      <c r="G314" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B315" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C315" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D315" t="str">
+        <v>2019</v>
+      </c>
+      <c r="E315">
+        <v>4560.3</v>
+      </c>
+      <c r="F315" t="str">
+        <v>A</v>
+      </c>
+      <c r="G315" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B316" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C316" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D316" t="str">
+        <v>2020</v>
+      </c>
+      <c r="E316">
+        <v>4978.2</v>
+      </c>
+      <c r="F316" t="str">
+        <v>A</v>
+      </c>
+      <c r="G316" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B317" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C317" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D317" t="str">
+        <v>2021</v>
+      </c>
+      <c r="E317">
+        <v>5081.3</v>
+      </c>
+      <c r="F317" t="str">
+        <v>A</v>
+      </c>
+      <c r="G317" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B318" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C318" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D318" t="str">
+        <v>2022</v>
+      </c>
+      <c r="E318">
+        <v>5688.3</v>
+      </c>
+      <c r="F318" t="str">
+        <v>A</v>
+      </c>
+      <c r="G318" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B319" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C319" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D319" t="str">
+        <v>2023</v>
+      </c>
+      <c r="E319">
+        <v>6720.1</v>
+      </c>
+      <c r="F319" t="str">
+        <v>A</v>
+      </c>
+      <c r="G319" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B320" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C320" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D320" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E320">
+        <v>7966.2</v>
+      </c>
+      <c r="F320" t="str">
+        <v>A</v>
+      </c>
+      <c r="G320" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B321" t="str">
+        <v>gfcf-other-buildings-and-structures</v>
+      </c>
+      <c r="C321" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D321" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E321">
+        <v>7858.3</v>
+      </c>
+      <c r="F321" t="str">
+        <v>P</v>
+      </c>
+      <c r="G321" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B322" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C322" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D322" t="str">
+        <v>2010</v>
+      </c>
+      <c r="E322">
+        <v>1292.5</v>
+      </c>
+      <c r="F322" t="str">
+        <v>A</v>
+      </c>
+      <c r="G322" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B323" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C323" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D323" t="str">
+        <v>2011</v>
+      </c>
+      <c r="E323">
+        <v>1902.6</v>
+      </c>
+      <c r="F323" t="str">
+        <v>A</v>
+      </c>
+      <c r="G323" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B324" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C324" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D324" t="str">
+        <v>2012</v>
+      </c>
+      <c r="E324">
+        <v>2189.8</v>
+      </c>
+      <c r="F324" t="str">
+        <v>A</v>
+      </c>
+      <c r="G324" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B325" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C325" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D325" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E325">
+        <v>2151.3</v>
+      </c>
+      <c r="F325" t="str">
+        <v>A</v>
+      </c>
+      <c r="G325" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B326" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C326" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D326" t="str">
+        <v>2014</v>
+      </c>
+      <c r="E326">
+        <v>2606.1</v>
+      </c>
+      <c r="F326" t="str">
+        <v>A</v>
+      </c>
+      <c r="G326" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B327" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C327" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D327" t="str">
+        <v>2015</v>
+      </c>
+      <c r="E327">
+        <v>2893.5</v>
+      </c>
+      <c r="F327" t="str">
+        <v>A</v>
+      </c>
+      <c r="G327" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B328" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C328" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D328" t="str">
+        <v>2016</v>
+      </c>
+      <c r="E328">
+        <v>3843.6</v>
+      </c>
+      <c r="F328" t="str">
+        <v>A</v>
+      </c>
+      <c r="G328" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B329" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C329" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D329" t="str">
+        <v>2017</v>
+      </c>
+      <c r="E329">
+        <v>4913.7</v>
+      </c>
+      <c r="F329" t="str">
+        <v>A</v>
+      </c>
+      <c r="G329" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B330" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C330" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D330" t="str">
+        <v>2018</v>
+      </c>
+      <c r="E330">
+        <v>4410.3</v>
+      </c>
+      <c r="F330" t="str">
+        <v>A</v>
+      </c>
+      <c r="G330" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B331" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C331" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D331" t="str">
+        <v>2019</v>
+      </c>
+      <c r="E331">
+        <v>3981.6</v>
+      </c>
+      <c r="F331" t="str">
+        <v>A</v>
+      </c>
+      <c r="G331" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B332" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C332" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D332" t="str">
+        <v>2020</v>
+      </c>
+      <c r="E332">
+        <v>3630.1</v>
+      </c>
+      <c r="F332" t="str">
+        <v>A</v>
+      </c>
+      <c r="G332" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B333" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C333" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D333" t="str">
+        <v>2021</v>
+      </c>
+      <c r="E333">
+        <v>4874.3</v>
+      </c>
+      <c r="F333" t="str">
+        <v>A</v>
+      </c>
+      <c r="G333" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B334" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C334" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D334" t="str">
+        <v>2022</v>
+      </c>
+      <c r="E334">
+        <v>5027.2</v>
+      </c>
+      <c r="F334" t="str">
+        <v>A</v>
+      </c>
+      <c r="G334" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B335" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C335" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D335" t="str">
+        <v>2023</v>
+      </c>
+      <c r="E335">
+        <v>5529.7</v>
+      </c>
+      <c r="F335" t="str">
+        <v>A</v>
+      </c>
+      <c r="G335" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B336" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C336" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D336" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E336">
+        <v>6255.9</v>
+      </c>
+      <c r="F336" t="str">
+        <v>A</v>
+      </c>
+      <c r="G336" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B337" t="str">
+        <v>gfcf-machinery-and-equipment</v>
+      </c>
+      <c r="C337" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D337" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E337">
+        <v>6484.5</v>
+      </c>
+      <c r="F337" t="str">
+        <v>P</v>
+      </c>
+      <c r="G337" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B338" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C338" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D338" t="str">
+        <v>2010</v>
+      </c>
+      <c r="E338">
+        <v>170.4</v>
+      </c>
+      <c r="F338" t="str">
+        <v>A</v>
+      </c>
+      <c r="G338" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B339" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C339" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D339" t="str">
+        <v>2011</v>
+      </c>
+      <c r="E339">
+        <v>226.1</v>
+      </c>
+      <c r="F339" t="str">
+        <v>A</v>
+      </c>
+      <c r="G339" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B340" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C340" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D340" t="str">
+        <v>2012</v>
+      </c>
+      <c r="E340">
+        <v>213</v>
+      </c>
+      <c r="F340" t="str">
+        <v>A</v>
+      </c>
+      <c r="G340" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B341" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C341" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D341" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E341">
+        <v>233.5</v>
+      </c>
+      <c r="F341" t="str">
+        <v>A</v>
+      </c>
+      <c r="G341" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B342" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C342" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D342" t="str">
+        <v>2014</v>
+      </c>
+      <c r="E342">
+        <v>312.5</v>
+      </c>
+      <c r="F342" t="str">
+        <v>A</v>
+      </c>
+      <c r="G342" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B343" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C343" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D343" t="str">
+        <v>2015</v>
+      </c>
+      <c r="E343">
+        <v>386.3</v>
+      </c>
+      <c r="F343" t="str">
+        <v>A</v>
+      </c>
+      <c r="G343" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B344" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C344" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D344" t="str">
+        <v>2016</v>
+      </c>
+      <c r="E344">
+        <v>390.3</v>
+      </c>
+      <c r="F344" t="str">
+        <v>A</v>
+      </c>
+      <c r="G344" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B345" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C345" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D345" t="str">
+        <v>2017</v>
+      </c>
+      <c r="E345">
+        <v>440.9</v>
+      </c>
+      <c r="F345" t="str">
+        <v>A</v>
+      </c>
+      <c r="G345" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B346" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C346" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D346" t="str">
+        <v>2018</v>
+      </c>
+      <c r="E346">
+        <v>435.1</v>
+      </c>
+      <c r="F346" t="str">
+        <v>A</v>
+      </c>
+      <c r="G346" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B347" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C347" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D347" t="str">
+        <v>2019</v>
+      </c>
+      <c r="E347">
+        <v>454.3</v>
+      </c>
+      <c r="F347" t="str">
+        <v>A</v>
+      </c>
+      <c r="G347" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B348" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C348" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D348" t="str">
+        <v>2020</v>
+      </c>
+      <c r="E348">
+        <v>543.9</v>
+      </c>
+      <c r="F348" t="str">
+        <v>A</v>
+      </c>
+      <c r="G348" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B349" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C349" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D349" t="str">
+        <v>2021</v>
+      </c>
+      <c r="E349">
+        <v>511.2</v>
+      </c>
+      <c r="F349" t="str">
+        <v>A</v>
+      </c>
+      <c r="G349" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B350" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C350" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D350" t="str">
+        <v>2022</v>
+      </c>
+      <c r="E350">
+        <v>561.8</v>
+      </c>
+      <c r="F350" t="str">
+        <v>A</v>
+      </c>
+      <c r="G350" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B351" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C351" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D351" t="str">
+        <v>2023</v>
+      </c>
+      <c r="E351">
+        <v>585.1</v>
+      </c>
+      <c r="F351" t="str">
+        <v>A</v>
+      </c>
+      <c r="G351" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B352" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C352" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D352" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E352">
+        <v>625.8</v>
+      </c>
+      <c r="F352" t="str">
+        <v>A</v>
+      </c>
+      <c r="G352" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B353" t="str">
+        <v>gfcf-cultivated-biological-resources</v>
+      </c>
+      <c r="C353" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D353" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E353">
+        <v>683.7</v>
+      </c>
+      <c r="F353" t="str">
+        <v>P</v>
+      </c>
+      <c r="G353" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B354" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C354" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D354" t="str">
+        <v>2010</v>
+      </c>
+      <c r="E354">
+        <v>115.2</v>
+      </c>
+      <c r="F354" t="str">
+        <v>A</v>
+      </c>
+      <c r="G354" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B355" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C355" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D355" t="str">
+        <v>2011</v>
+      </c>
+      <c r="E355">
+        <v>100.2</v>
+      </c>
+      <c r="F355" t="str">
+        <v>A</v>
+      </c>
+      <c r="G355" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B356" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C356" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D356" t="str">
+        <v>2012</v>
+      </c>
+      <c r="E356">
+        <v>272.7</v>
+      </c>
+      <c r="F356" t="str">
+        <v>A</v>
+      </c>
+      <c r="G356" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B357" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C357" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D357" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E357">
+        <v>140.7</v>
+      </c>
+      <c r="F357" t="str">
+        <v>A</v>
+      </c>
+      <c r="G357" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B358" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C358" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D358" t="str">
+        <v>2014</v>
+      </c>
+      <c r="E358">
+        <v>160.8</v>
+      </c>
+      <c r="F358" t="str">
+        <v>A</v>
+      </c>
+      <c r="G358" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B359" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C359" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D359" t="str">
+        <v>2015</v>
+      </c>
+      <c r="E359">
+        <v>805.7</v>
+      </c>
+      <c r="F359" t="str">
+        <v>A</v>
+      </c>
+      <c r="G359" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B360" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C360" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D360" t="str">
+        <v>2016</v>
+      </c>
+      <c r="E360">
+        <v>422.1</v>
+      </c>
+      <c r="F360" t="str">
+        <v>A</v>
+      </c>
+      <c r="G360" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B361" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C361" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D361" t="str">
+        <v>2017</v>
+      </c>
+      <c r="E361">
+        <v>286.8</v>
+      </c>
+      <c r="F361" t="str">
+        <v>A</v>
+      </c>
+      <c r="G361" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B362" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C362" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D362" t="str">
+        <v>2018</v>
+      </c>
+      <c r="E362">
+        <v>354.6</v>
+      </c>
+      <c r="F362" t="str">
+        <v>A</v>
+      </c>
+      <c r="G362" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B363" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C363" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D363" t="str">
+        <v>2019</v>
+      </c>
+      <c r="E363">
+        <v>423.8</v>
+      </c>
+      <c r="F363" t="str">
+        <v>A</v>
+      </c>
+      <c r="G363" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B364" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C364" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D364" t="str">
+        <v>2020</v>
+      </c>
+      <c r="E364">
+        <v>429.5</v>
+      </c>
+      <c r="F364" t="str">
+        <v>A</v>
+      </c>
+      <c r="G364" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B365" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C365" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D365" t="str">
+        <v>2021</v>
+      </c>
+      <c r="E365">
+        <v>641.7</v>
+      </c>
+      <c r="F365" t="str">
+        <v>A</v>
+      </c>
+      <c r="G365" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B366" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C366" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D366" t="str">
+        <v>2022</v>
+      </c>
+      <c r="E366">
+        <v>457.3</v>
+      </c>
+      <c r="F366" t="str">
+        <v>A</v>
+      </c>
+      <c r="G366" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B367" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C367" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D367" t="str">
+        <v>2023</v>
+      </c>
+      <c r="E367">
+        <v>663.8</v>
+      </c>
+      <c r="F367" t="str">
+        <v>A</v>
+      </c>
+      <c r="G367" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B368" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C368" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D368" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E368">
+        <v>355.6</v>
+      </c>
+      <c r="F368" t="str">
+        <v>A</v>
+      </c>
+      <c r="G368" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>GFCF</v>
+      </c>
+      <c r="B369" t="str">
+        <v>gfcf-intellectual-property-products</v>
+      </c>
+      <c r="C369" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D369" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E369">
+        <v>569.6</v>
+      </c>
+      <c r="F369" t="str">
+        <v>P</v>
+      </c>
+      <c r="G369" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B370" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C370" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D370" t="str">
+        <v>2010</v>
+      </c>
+      <c r="E370">
+        <v>23.1</v>
+      </c>
+      <c r="F370" t="str">
+        <v>A</v>
+      </c>
+      <c r="G370" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B371" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C371" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D371" t="str">
+        <v>2011</v>
+      </c>
+      <c r="E371">
+        <v>20.8</v>
+      </c>
+      <c r="F371" t="str">
+        <v>A</v>
+      </c>
+      <c r="G371" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B372" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C372" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D372" t="str">
+        <v>2012</v>
+      </c>
+      <c r="E372">
+        <v>17.7</v>
+      </c>
+      <c r="F372" t="str">
+        <v>A</v>
+      </c>
+      <c r="G372" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B373" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C373" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D373" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E373">
+        <v>14.8</v>
+      </c>
+      <c r="F373" t="str">
+        <v>A</v>
+      </c>
+      <c r="G373" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B374" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C374" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D374" t="str">
+        <v>2014</v>
+      </c>
+      <c r="E374">
+        <v>15.1</v>
+      </c>
+      <c r="F374" t="str">
+        <v>A</v>
+      </c>
+      <c r="G374" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B375" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C375" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D375" t="str">
+        <v>2015</v>
+      </c>
+      <c r="E375">
+        <v>13.6</v>
+      </c>
+      <c r="F375" t="str">
+        <v>A</v>
+      </c>
+      <c r="G375" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B376" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C376" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D376" t="str">
+        <v>2016</v>
+      </c>
+      <c r="E376">
+        <v>12.7</v>
+      </c>
+      <c r="F376" t="str">
+        <v>A</v>
+      </c>
+      <c r="G376" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B377" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C377" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D377" t="str">
+        <v>2017</v>
+      </c>
+      <c r="E377">
+        <v>13.4</v>
+      </c>
+      <c r="F377" t="str">
+        <v>A</v>
+      </c>
+      <c r="G377" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B378" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C378" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D378" t="str">
+        <v>2018</v>
+      </c>
+      <c r="E378">
+        <v>13.3</v>
+      </c>
+      <c r="F378" t="str">
+        <v>A</v>
+      </c>
+      <c r="G378" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B379" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C379" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D379" t="str">
+        <v>2019</v>
+      </c>
+      <c r="E379">
+        <v>14.3</v>
+      </c>
+      <c r="F379" t="str">
+        <v>A</v>
+      </c>
+      <c r="G379" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B380" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C380" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D380" t="str">
+        <v>2020</v>
+      </c>
+      <c r="E380">
+        <v>12.8</v>
+      </c>
+      <c r="F380" t="str">
+        <v>A</v>
+      </c>
+      <c r="G380" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B381" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C381" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D381" t="str">
+        <v>2021</v>
+      </c>
+      <c r="E381">
+        <v>14.4</v>
+      </c>
+      <c r="F381" t="str">
+        <v>A</v>
+      </c>
+      <c r="G381" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B382" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C382" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D382" t="str">
+        <v>2022</v>
+      </c>
+      <c r="E382">
+        <v>13.1</v>
+      </c>
+      <c r="F382" t="str">
+        <v>A</v>
+      </c>
+      <c r="G382" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B383" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C383" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D383" t="str">
+        <v>2023</v>
+      </c>
+      <c r="E383">
+        <v>12.4</v>
+      </c>
+      <c r="F383" t="str">
+        <v>A</v>
+      </c>
+      <c r="G383" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B384" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C384" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D384" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E384">
+        <v>12.5</v>
+      </c>
+      <c r="F384" t="str">
+        <v>A</v>
+      </c>
+      <c r="G384" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B385" t="str">
+        <v>non-observed-economy-share</v>
+      </c>
+      <c r="C385" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D385" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E385">
+        <v>12.4</v>
+      </c>
+      <c r="F385" t="str">
+        <v>P</v>
+      </c>
+      <c r="G385" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G289"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G385"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/DATA/canonical/GDP_ANNUAL.xlsx
+++ b/DATA/canonical/GDP_ANNUAL.xlsx
@@ -36,10 +36,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -474,7 +472,7 @@
         <v>vintage</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-26</v>
+        <v>2026-07-03</v>
       </c>
     </row>
   </sheetData>
@@ -599,7 +597,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -992,9 +990,26 @@
         <v>22</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="B24" t="str">
+        <v>მშპ დეფლატორი</v>
+      </c>
+      <c r="C24" t="str">
+        <v>GDP deflator, annual % change</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E24"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1046,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G385"/>
+  <dimension ref="A1:G400"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9903,9 +9918,354 @@
         <v/>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B386" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C386" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D386" t="str">
+        <v>2011</v>
+      </c>
+      <c r="E386">
+        <v>9.160005309089456</v>
+      </c>
+      <c r="F386" t="str">
+        <v>A</v>
+      </c>
+      <c r="G386" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B387" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C387" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D387" t="str">
+        <v>2012</v>
+      </c>
+      <c r="E387">
+        <v>0.28900496137659104</v>
+      </c>
+      <c r="F387" t="str">
+        <v>A</v>
+      </c>
+      <c r="G387" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B388" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C388" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D388" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E388">
+        <v>-0.6520077299118725</v>
+      </c>
+      <c r="F388" t="str">
+        <v>A</v>
+      </c>
+      <c r="G388" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B389" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C389" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D389" t="str">
+        <v>2014</v>
+      </c>
+      <c r="E389">
+        <v>4.592080146792156</v>
+      </c>
+      <c r="F389" t="str">
+        <v>A</v>
+      </c>
+      <c r="G389" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B390" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C390" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D390" t="str">
+        <v>2015</v>
+      </c>
+      <c r="E390">
+        <v>5.376813283499672</v>
+      </c>
+      <c r="F390" t="str">
+        <v>A</v>
+      </c>
+      <c r="G390" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B391" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C391" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D391" t="str">
+        <v>2016</v>
+      </c>
+      <c r="E391">
+        <v>2.2754508620340204</v>
+      </c>
+      <c r="F391" t="str">
+        <v>A</v>
+      </c>
+      <c r="G391" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B392" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C392" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D392" t="str">
+        <v>2017</v>
+      </c>
+      <c r="E392">
+        <v>7.544042841121339</v>
+      </c>
+      <c r="F392" t="str">
+        <v>A</v>
+      </c>
+      <c r="G392" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B393" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C393" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D393" t="str">
+        <v>2018</v>
+      </c>
+      <c r="E393">
+        <v>3.4860683230616303</v>
+      </c>
+      <c r="F393" t="str">
+        <v>A</v>
+      </c>
+      <c r="G393" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B394" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C394" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D394" t="str">
+        <v>2019</v>
+      </c>
+      <c r="E394">
+        <v>3.9958884199483293</v>
+      </c>
+      <c r="F394" t="str">
+        <v>A</v>
+      </c>
+      <c r="G394" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B395" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C395" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D395" t="str">
+        <v>2020</v>
+      </c>
+      <c r="E395">
+        <v>6.847224256112398</v>
+      </c>
+      <c r="F395" t="str">
+        <v>A</v>
+      </c>
+      <c r="G395" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B396" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C396" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D396" t="str">
+        <v>2021</v>
+      </c>
+      <c r="E396">
+        <v>10.231083876544915</v>
+      </c>
+      <c r="F396" t="str">
+        <v>A</v>
+      </c>
+      <c r="G396" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B397" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C397" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D397" t="str">
+        <v>2022</v>
+      </c>
+      <c r="E397">
+        <v>8.134307711093811</v>
+      </c>
+      <c r="F397" t="str">
+        <v>A</v>
+      </c>
+      <c r="G397" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B398" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C398" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D398" t="str">
+        <v>2023</v>
+      </c>
+      <c r="E398">
+        <v>2.948473043458378</v>
+      </c>
+      <c r="F398" t="str">
+        <v>A</v>
+      </c>
+      <c r="G398" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B399" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C399" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D399" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E399">
+        <v>4.858673860498129</v>
+      </c>
+      <c r="F399" t="str">
+        <v>A</v>
+      </c>
+      <c r="G399" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>_Z</v>
+      </c>
+      <c r="B400" t="str">
+        <v>gdp-deflator</v>
+      </c>
+      <c r="C400" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D400" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E400">
+        <v>4.636605038644404</v>
+      </c>
+      <c r="F400" t="str">
+        <v>P</v>
+      </c>
+      <c r="G400" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G385"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G400"/>
   </ignoredErrors>
 </worksheet>
 </file>